--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90756</v>
+        <v>90761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90756</v>
+        <v>90761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90776</v>
+        <v>90777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90776</v>
+        <v>90777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49701-2023 artfynd.xlsx
+++ b/artfynd/A 49701-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934861</v>
       </c>
       <c r="B2" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136934862</v>
       </c>
       <c r="B3" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136934863</v>
       </c>
       <c r="B4" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136934864</v>
       </c>
       <c r="B5" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>136934875</v>
       </c>
       <c r="B6" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136934860</v>
       </c>
       <c r="B7" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136934868</v>
       </c>
       <c r="B8" t="n">
-        <v>90777</v>
+        <v>90780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136934873</v>
       </c>
       <c r="B9" t="n">
-        <v>90777</v>
+        <v>90780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>136934865</v>
       </c>
       <c r="B10" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
